--- a/artfynd/A 25480-2025 artfynd.xlsx
+++ b/artfynd/A 25480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5473418</v>
       </c>
       <c r="B2" t="n">
-        <v>100778</v>
+        <v>100780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25480-2025 artfynd.xlsx
+++ b/artfynd/A 25480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5473418</v>
       </c>
       <c r="B2" t="n">
-        <v>100780</v>
+        <v>100867</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25480-2025 artfynd.xlsx
+++ b/artfynd/A 25480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5473418</v>
       </c>
       <c r="B2" t="n">
-        <v>100867</v>
+        <v>100870</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25480-2025 artfynd.xlsx
+++ b/artfynd/A 25480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5473418</v>
       </c>
       <c r="B2" t="n">
-        <v>100870</v>
+        <v>100896</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25480-2025 artfynd.xlsx
+++ b/artfynd/A 25480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5473418</v>
       </c>
       <c r="B2" t="n">
-        <v>100896</v>
+        <v>100897</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25480-2025 artfynd.xlsx
+++ b/artfynd/A 25480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5473418</v>
       </c>
       <c r="B2" t="n">
-        <v>100897</v>
+        <v>100898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25480-2025 artfynd.xlsx
+++ b/artfynd/A 25480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5473418</v>
       </c>
       <c r="B2" t="n">
-        <v>100898</v>
+        <v>100900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25480-2025 artfynd.xlsx
+++ b/artfynd/A 25480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5473418</v>
       </c>
       <c r="B2" t="n">
-        <v>100900</v>
+        <v>100904</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25480-2025 artfynd.xlsx
+++ b/artfynd/A 25480-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5473418</v>
+        <v>5460012</v>
       </c>
       <c r="B2" t="n">
-        <v>100904</v>
+        <v>101079</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -703,16 +703,7 @@
           <t>(L.) Schweigg. &amp; Körte</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rövarkulans naturreservat. Lilla Västraby, 1,4 km väster, Sk</t>
@@ -754,12 +745,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-04-22</t>
+          <t>1992-04-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-04-22</t>
+          <t>1992-04-24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2D7b2501</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +780,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Nihlgård</t>
+          <t>Kjell-arne Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
